--- a/field_data/TOPOLOGY.xlsx
+++ b/field_data/TOPOLOGY.xlsx
@@ -843,7 +843,7 @@
     <row r="41" ht="42" customHeight="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>When NODES is complete, the generator can be extended to draw the real trunk and spurs instead of inferring them. This workbook is the collection format; the reader is the next code step. See TOPOLOGY_DATA_REQUIREMENTS.md for the reasoning and the optional extras.</t>
+          <t>When NODES is complete, the generator can be extended to draw the real trunk and spurs instead of inferring them. This workbook is the collection format; the reader is the next code step. See docs/TOPOLOGY_DATA_REQUIREMENTS.md for the reasoning and the optional extras.</t>
         </is>
       </c>
     </row>
